--- a/data/radar_template-2.xlsx
+++ b/data/radar_template-2.xlsx
@@ -599,7 +599,7 @@
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
